--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -470,7 +470,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0</t>
   </si>
   <si>
     <t>Encounter.meta.security</t>
@@ -638,7 +638,7 @@
     <t>estimatedDischargeDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date|2.2.0}
 </t>
   </si>
   <si>
@@ -748,7 +748,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type|2.2.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -834,7 +834,7 @@
     <t>Encounter.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1130,7 +1130,7 @@
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type|2.2.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1188,7 +1188,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0-ballot-2|Group|4.0.1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1327,7 +1327,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0-ballot-2|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1352,7 +1352,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.2.0)
 </t>
   </si>
   <si>
@@ -1630,7 +1630,7 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0-ballot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1775,7 +1775,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition|2.2.0</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1811,7 +1811,7 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
 </t>
   </si>
   <si>
@@ -1864,7 +1864,7 @@
 There may be many levels in the hierachy, and this may only pic specific levels that are required for a specific usage scenario.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-type|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-type|2.2.0</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -1894,7 +1894,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>
@@ -2235,7 +2235,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="130.15625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="117.0625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2250,7 +2250,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="72.30859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.76171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -7972,7 +7972,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
